--- a/AlgoTradingPython/config/configMeanRevertPortEOD.xlsx
+++ b/AlgoTradingPython/config/configMeanRevertPortEOD.xlsx
@@ -401,7 +401,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.07"/>
@@ -480,7 +480,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -1457,7 +1457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -1500,7 +1500,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.3"/>
   </cols>
@@ -1534,7 +1534,7 @@
         <v>81</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1606,7 +1606,7 @@
         <v>91</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/AlgoTradingPython/config/configMeanRevertPortEOD.xlsx
+++ b/AlgoTradingPython/config/configMeanRevertPortEOD.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="95">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -299,6 +299,15 @@
   </si>
   <si>
     <t xml:space="preserve">money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hurst level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half-life lower limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA multiplication</t>
   </si>
 </sst>
 </file>
@@ -401,7 +410,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.07"/>
@@ -480,7 +489,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -1457,7 +1466,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -1499,10 +1508,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,6 +1616,38 @@
       </c>
       <c r="B13" s="0" t="n">
         <v>200</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>0.361702921601312</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>62.3571118812026</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>3.02843409246134</v>
       </c>
     </row>
   </sheetData>
